--- a/data/trans_dic/P33_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P33_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,32; 16,61</t>
+          <t>11,12; 16,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,62; 31,45</t>
+          <t>24,53; 31,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,97; 24,46</t>
+          <t>18,17; 24,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,62; 25,37</t>
+          <t>19,32; 26,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,08; 22,22</t>
+          <t>16,19; 22,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,48; 36,59</t>
+          <t>29,3; 36,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,48; 34,8</t>
+          <t>27,44; 34,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,29; 35,96</t>
+          <t>30,0; 35,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 18,57</t>
+          <t>14,43; 18,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,03; 33,17</t>
+          <t>28,05; 32,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,82; 28,67</t>
+          <t>23,71; 28,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,22; 29,75</t>
+          <t>25,53; 29,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 23,44</t>
+          <t>17,88; 23,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,66; 29,16</t>
+          <t>23,35; 29,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 22,23</t>
+          <t>16,98; 22,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 22,21</t>
+          <t>17,81; 23,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,27; 27,05</t>
+          <t>21,41; 27,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,9; 36,99</t>
+          <t>31,04; 37,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,42; 30,25</t>
+          <t>24,37; 30,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,17; 29,07</t>
+          <t>24,22; 28,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,57; 24,69</t>
+          <t>20,72; 24,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,23; 32,57</t>
+          <t>28,26; 32,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,58; 25,39</t>
+          <t>21,59; 25,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 24,74</t>
+          <t>21,63; 25,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 23,52</t>
+          <t>16,95; 23,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,49; 26,18</t>
+          <t>19,2; 25,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,91; 29,63</t>
+          <t>22,99; 29,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,08; 31,61</t>
+          <t>23,68; 30,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,75; 33,83</t>
+          <t>27,03; 34,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,07; 32,71</t>
+          <t>26,15; 32,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,35; 33,95</t>
+          <t>27,26; 34,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,11; 69,4</t>
+          <t>27,3; 33,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,82; 27,42</t>
+          <t>22,97; 27,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,71; 28,33</t>
+          <t>23,66; 28,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,1; 30,78</t>
+          <t>26,16; 30,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,57; 61,19</t>
+          <t>26,2; 31,14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 21,5</t>
+          <t>16,32; 21,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,07; 30,01</t>
+          <t>23,87; 29,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,53; 29,29</t>
+          <t>23,59; 29,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,17; 31,52</t>
+          <t>25,15; 31,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 25,95</t>
+          <t>20,75; 26,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,87; 35,67</t>
+          <t>30,2; 35,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,95; 29,7</t>
+          <t>23,82; 29,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,45; 34,45</t>
+          <t>31,57; 36,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 22,87</t>
+          <t>19,33; 23,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,87; 32,08</t>
+          <t>27,97; 32,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,58; 28,51</t>
+          <t>24,34; 28,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,25; 32,12</t>
+          <t>29,2; 33,01</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 20,02</t>
+          <t>17,16; 20,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,38; 27,59</t>
+          <t>24,21; 27,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,51; 24,65</t>
+          <t>21,7; 24,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 25,73</t>
+          <t>22,96; 26,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,67; 25,58</t>
+          <t>22,68; 25,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,97; 34,37</t>
+          <t>30,84; 34,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,96; 30,1</t>
+          <t>26,98; 30,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,45; 46,78</t>
+          <t>29,43; 32,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,39; 22,39</t>
+          <t>20,32; 22,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,05; 30,32</t>
+          <t>28,27; 30,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,85; 27,06</t>
+          <t>24,81; 27,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,42; 35,64</t>
+          <t>26,65; 28,7</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135226</t>
+          <t>151528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>217579</t>
+          <t>232408</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>352805</t>
+          <t>383935</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>77530; 113800</t>
+          <t>76180; 111696</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>172918; 220939</t>
+          <t>172289; 218334</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120603; 164215</t>
+          <t>121978; 165093</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115855; 157792</t>
+          <t>130651; 176553</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>110230; 152362</t>
+          <t>111017; 151659</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>205157; 254631</t>
+          <t>203908; 254986</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>182591; 231246</t>
+          <t>182326; 228212</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>198856; 236125</t>
+          <t>213895; 251978</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>198513; 254575</t>
+          <t>197848; 250979</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>391981; 463847</t>
+          <t>392238; 461111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>318175; 382987</t>
+          <t>316744; 380636</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>322523; 380336</t>
+          <t>354656; 415856</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>197133</t>
+          <t>209772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>270647</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>442920</t>
+          <t>480419</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>170561; 222607</t>
+          <t>169767; 223635</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>240359; 296296</t>
+          <t>237212; 296710</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173881; 226537</t>
+          <t>173010; 224919</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88047; 258223</t>
+          <t>181946; 236641</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>204673; 260332</t>
+          <t>205982; 261089</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>318606; 381398</t>
+          <t>320042; 383978</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>254175; 314815</t>
+          <t>253668; 313828</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>222191; 267203</t>
+          <t>249319; 296592</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>393324; 472114</t>
+          <t>396106; 468049</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>577947; 666788</t>
+          <t>578571; 667951</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>444484; 522942</t>
+          <t>444748; 526044</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>292241; 515047</t>
+          <t>443570; 515133</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>179637</t>
+          <t>202219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>406440</t>
+          <t>232792</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>586077</t>
+          <t>435010</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>114338; 157719</t>
+          <t>113672; 155619</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>147236; 197854</t>
+          <t>145102; 196062</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174002; 225021</t>
+          <t>174651; 225132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>155612; 204241</t>
+          <t>175594; 229294</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>181267; 229179</t>
+          <t>183126; 230955</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>202365; 253926</t>
+          <t>202985; 255291</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>214450; 266159</t>
+          <t>213748; 271080</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>251135; 620018</t>
+          <t>209626; 254471</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>307628; 369694</t>
+          <t>309720; 372315</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>363165; 433979</t>
+          <t>362379; 434718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>402902; 475055</t>
+          <t>403882; 478279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>424421; 941937</t>
+          <t>395416; 470111</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262706</t>
+          <t>276728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>341188</t>
+          <t>377228</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>603895</t>
+          <t>653956</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>150642; 198713</t>
+          <t>150860; 196988</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>226124; 281956</t>
+          <t>224322; 281020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>220619; 274593</t>
+          <t>221143; 277646</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>233052; 291840</t>
+          <t>248748; 307721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>212920; 267723</t>
+          <t>214112; 269537</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>312356; 373019</t>
+          <t>315778; 373001</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>249209; 309068</t>
+          <t>247842; 308038</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>277161; 375194</t>
+          <t>351405; 407634</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>377252; 447362</t>
+          <t>378179; 450177</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>553316; 636972</t>
+          <t>555278; 636413</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>486262; 563994</t>
+          <t>481437; 563992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>528940; 647222</t>
+          <t>613875; 693924</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>774702</t>
+          <t>840246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1210995</t>
+          <t>1113074</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1985697</t>
+          <t>1953320</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>555227; 646675</t>
+          <t>554047; 649763</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>832387; 941945</t>
+          <t>826532; 934936</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>728777; 834909</t>
+          <t>735103; 838273</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>592845; 863876</t>
+          <t>787282; 894029</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>760929; 858862</t>
+          <t>761366; 861081</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1099157; 1219663</t>
+          <t>1094611; 1216383</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>951601; 1062651</t>
+          <t>952532; 1062267</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1047790; 1664509</t>
+          <t>1066597; 1169690</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1342973; 1474587</t>
+          <t>1338686; 1468943</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1952772; 2111054</t>
+          <t>1968252; 2120077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1718801; 1871601</t>
+          <t>1716459; 1870789</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1757557; 2464388</t>
+          <t>1879397; 2023902</t>
         </is>
       </c>
     </row>
